--- a/medical_surveys_questionnaires/007_cardiology_consultation_form--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/007_cardiology_consultation_form--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -908,8 +908,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -937,12 +937,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'only_with_exertion',_'value':_'exertion'}</t>
+          <t>only_with_exertion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Only with exertion', 'value': 'exertion'}</t>
+          <t>Only with exertion</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'at_rest',_'value':_'rest'}</t>
+          <t>at_rest</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'At rest', 'value': 'rest'}</t>
+          <t>At rest</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'during_sleep',_'value':_'sleep'}</t>
+          <t>during_sleep</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'During sleep', 'value': 'sleep'}</t>
+          <t>During sleep</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure',_'value':_'unknown'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure', 'value': 'unknown'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'current_smoker',_'value':_'current'}</t>
+          <t>current_smoker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Current Smoker', 'value': 'current'}</t>
+          <t>Current Smoker</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'former_smoker',_'value':_'former'}</t>
+          <t>former_smoker</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Former Smoker', 'value': 'former'}</t>
+          <t>Former Smoker</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'never_smoked',_'value':_'never'}</t>
+          <t>never_smoked</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Never Smoked', 'value': 'never'}</t>
+          <t>Never Smoked</t>
         </is>
       </c>
     </row>
